--- a/test/Volume_test.xlsx
+++ b/test/Volume_test.xlsx
@@ -10,12 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{7E68086D-2699-6647-A8B0-110B03CAC8BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{71C80BD2-67E0-A840-BA28-32573E024477}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17020" xr2:uid="{71C80BD2-67E0-A840-BA28-32573E024477}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -175,18 +175,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -543,10 +541,10 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -554,23 +552,23 @@
       <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2">
         <f>(A15+B17+C18+D19+E20)/5</f>
         <v>16.8</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <f>F2*12*2*8*5*40</f>
         <v>645120.00000000012</v>
       </c>
@@ -579,321 +577,301 @@
       <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3">
         <v>2</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4">
         <v>3</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4">
         <v>3</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="5"/>
+      <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>4</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>4</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5">
         <v>4</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5"/>
+      <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>5</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6">
         <v>5</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="5"/>
+      <c r="G6" s="4"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>6</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7">
         <v>6</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7">
         <v>6</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="4"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8">
         <v>7</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8">
         <v>7</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="5"/>
+      <c r="G8" s="4"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>8</v>
       </c>
-      <c r="C9" s="4">
+      <c r="C9">
         <v>8</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9">
         <v>8</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9">
         <v>8</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10">
         <v>9</v>
       </c>
-      <c r="C10" s="4">
+      <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10">
         <v>9</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10">
         <v>9</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11">
         <v>10</v>
       </c>
-      <c r="C11" s="4">
+      <c r="C11">
         <v>10</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11">
         <v>10</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11">
         <v>10</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="5"/>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12">
         <v>11</v>
       </c>
-      <c r="C12" s="4">
+      <c r="C12">
         <v>11</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12">
         <v>11</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12">
         <v>11</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="5"/>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13">
         <v>12</v>
       </c>
-      <c r="C13" s="4">
+      <c r="C13">
         <v>12</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13">
         <v>12</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13">
         <v>12</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="5"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>13</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14">
         <v>13</v>
       </c>
-      <c r="C14" s="4">
+      <c r="C14">
         <v>13</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14">
         <v>13</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14">
         <v>13</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="5"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="4">
+      <c r="B15">
         <v>14</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15">
         <v>14</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15">
         <v>14</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15">
         <v>14</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="5"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="3"/>
-      <c r="B16" s="4">
+      <c r="B16">
         <v>15</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16">
         <v>15</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16">
         <v>15</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16">
         <v>15</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="5"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="3"/>
-      <c r="B17" s="4">
+      <c r="B17">
         <v>16</v>
       </c>
-      <c r="C17" s="4">
+      <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17">
         <v>16</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17">
         <v>16</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="5"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="3"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4">
+      <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18">
         <v>17</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18">
         <v>17</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="5"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4">
+      <c r="D19">
         <v>18</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19">
         <v>18</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="5"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7">
+      <c r="A20" s="5"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6">
         <v>19</v>
       </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="8"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
